--- a/Data/Export/Common/AttributeChangeType_能力变化类型.xlsx
+++ b/Data/Export/Common/AttributeChangeType_能力变化类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616B1198-54CD-41C5-87A2-2DE8BDC87172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9B0FF6-4D05-426E-ABAF-62B23C5A3C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2088" yWindow="3984" windowWidth="18216" windowHeight="11796" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeChangeTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -102,6 +102,10 @@
   </si>
   <si>
     <t>张飞型</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -582,25 +586,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:U69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="26.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="89.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="71.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="89.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="71.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="11" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -627,7 +631,7 @@
       <c r="T1" s="9"/>
       <c r="U1" s="7"/>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -652,7 +656,7 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -683,7 +687,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:21" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -700,12 +704,12 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -720,12 +724,12 @@
       <c r="R5" s="4"/>
       <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -740,13 +744,12 @@
       <c r="R6" s="4"/>
       <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4">
-        <v>3</v>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="B7" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -761,12 +764,13 @@
       <c r="R7" s="4"/>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A8" s="3"/>
       <c r="B8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -781,12 +785,12 @@
       <c r="R8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -801,12 +805,12 @@
       <c r="R9" s="4"/>
       <c r="T9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -821,12 +825,12 @@
       <c r="R10" s="4"/>
       <c r="T10" s="4"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -841,12 +845,12 @@
       <c r="R11" s="4"/>
       <c r="T11" s="4"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -861,12 +865,12 @@
       <c r="R12" s="4"/>
       <c r="T12" s="4"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -881,9 +885,13 @@
       <c r="R13" s="4"/>
       <c r="T13" s="4"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="B14" s="4">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="I14" s="6"/>
@@ -897,7 +905,7 @@
       <c r="R14" s="4"/>
       <c r="T14" s="4"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -913,7 +921,7 @@
       <c r="R15" s="4"/>
       <c r="T15" s="4"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -929,7 +937,7 @@
       <c r="R16" s="4"/>
       <c r="T16" s="4"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -945,7 +953,7 @@
       <c r="R17" s="4"/>
       <c r="T17" s="4"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -961,7 +969,7 @@
       <c r="R18" s="4"/>
       <c r="T18" s="4"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -977,7 +985,7 @@
       <c r="R19" s="4"/>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -993,7 +1001,7 @@
       <c r="R20" s="4"/>
       <c r="T20" s="4"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1009,7 +1017,7 @@
       <c r="R21" s="4"/>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1025,7 +1033,7 @@
       <c r="R22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1041,7 +1049,7 @@
       <c r="R23" s="4"/>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1057,7 +1065,7 @@
       <c r="R24" s="4"/>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1073,7 +1081,7 @@
       <c r="R25" s="4"/>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1089,7 +1097,7 @@
       <c r="R26" s="4"/>
       <c r="T26" s="4"/>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1105,7 +1113,7 @@
       <c r="R27" s="4"/>
       <c r="T27" s="4"/>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1121,7 +1129,7 @@
       <c r="R28" s="4"/>
       <c r="T28" s="4"/>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1137,7 +1145,7 @@
       <c r="R29" s="4"/>
       <c r="T29" s="4"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -1153,7 +1161,7 @@
       <c r="R30" s="4"/>
       <c r="T30" s="4"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1169,7 +1177,7 @@
       <c r="R31" s="4"/>
       <c r="T31" s="4"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -1185,7 +1193,7 @@
       <c r="R32" s="4"/>
       <c r="T32" s="4"/>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1201,7 +1209,7 @@
       <c r="R33" s="4"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -1217,7 +1225,7 @@
       <c r="R34" s="4"/>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1233,7 +1241,7 @@
       <c r="R35" s="4"/>
       <c r="T35" s="4"/>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1249,10 +1257,12 @@
       <c r="R36" s="4"/>
       <c r="T36" s="4"/>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
+      <c r="I37" s="6"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1263,10 +1273,10 @@
       <c r="R37" s="4"/>
       <c r="T37" s="4"/>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.15">
+      <c r="B38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="I38" s="6"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1277,7 +1287,7 @@
       <c r="R38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="I39" s="6"/>
@@ -1291,7 +1301,7 @@
       <c r="R39" s="4"/>
       <c r="T39" s="4"/>
     </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="I40" s="6"/>
@@ -1305,7 +1315,7 @@
       <c r="R40" s="4"/>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="I41" s="6"/>
@@ -1319,7 +1329,7 @@
       <c r="R41" s="4"/>
       <c r="T41" s="4"/>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="I42" s="6"/>
@@ -1333,7 +1343,7 @@
       <c r="R42" s="4"/>
       <c r="T42" s="4"/>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="I43" s="6"/>
@@ -1347,7 +1357,7 @@
       <c r="R43" s="4"/>
       <c r="T43" s="4"/>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="I44" s="6"/>
@@ -1361,7 +1371,7 @@
       <c r="R44" s="4"/>
       <c r="T44" s="4"/>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="I45" s="6"/>
@@ -1375,7 +1385,7 @@
       <c r="R45" s="4"/>
       <c r="T45" s="4"/>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="I46" s="6"/>
@@ -1385,18 +1395,24 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
       <c r="T46" s="4"/>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
+      <c r="I47" s="6"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="T47" s="4"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="J48" s="4"/>
@@ -1404,7 +1420,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="J49" s="4"/>
@@ -1412,7 +1428,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="J50" s="4"/>
@@ -1420,7 +1436,7 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="J51" s="4"/>
@@ -1428,7 +1444,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="J52" s="4"/>
@@ -1436,7 +1452,7 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="J53" s="4"/>
@@ -1444,7 +1460,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="J54" s="4"/>
@@ -1452,7 +1468,7 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="J55" s="4"/>
@@ -1460,7 +1476,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="J56" s="4"/>
@@ -1468,7 +1484,7 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
     </row>
-    <row r="57" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="J57" s="4"/>
@@ -1476,7 +1492,7 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
     </row>
-    <row r="58" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="J58" s="4"/>
@@ -1484,7 +1500,7 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
     </row>
-    <row r="59" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="J59" s="4"/>
@@ -1492,7 +1508,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
     </row>
-    <row r="60" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="J60" s="4"/>
@@ -1500,7 +1516,7 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
     </row>
-    <row r="61" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="J61" s="4"/>
@@ -1508,7 +1524,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
     </row>
-    <row r="62" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="J62" s="4"/>
@@ -1516,7 +1532,7 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="J63" s="4"/>
@@ -1524,7 +1540,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="J64" s="4"/>
@@ -1532,7 +1548,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="J65" s="4"/>
@@ -1540,7 +1556,7 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="J66" s="4"/>
@@ -1548,7 +1564,7 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
     </row>
-    <row r="67" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="J67" s="4"/>
@@ -1556,7 +1572,7 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="J68" s="4"/>
@@ -1564,8 +1580,16 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:13" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+    </row>
+    <row r="70" spans="4:13" x14ac:dyDescent="0.15">
+      <c r="D70" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
